--- a/artfynd/A 36982-2023 artfynd.xlsx
+++ b/artfynd/A 36982-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 36982-2023 artfynd.xlsx
+++ b/artfynd/A 36982-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AY11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1764,6 +1764,108 @@
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>120397453</v>
+      </c>
+      <c r="B11" t="n">
+        <v>56524</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>102612</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Järpe</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Tetrastes bonasia</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Nattavara, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>751652</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7424472</v>
+      </c>
+      <c r="S11" t="n">
+        <v>5</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2024-07-23</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2024-07-23</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Hanna Emanuelsson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Hanna Emanuelsson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 36982-2023 artfynd.xlsx
+++ b/artfynd/A 36982-2023 artfynd.xlsx
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>61639784</v>
+        <v>61639719</v>
       </c>
       <c r="B2" t="n">
-        <v>86948</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92183</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4962</v>
+        <v>65</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mjölsvärting</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lyophyllum semitale</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr. : Fr.) Kühner</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -721,14 +716,14 @@
       <c r="K2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Stenbäcken, Lu lm</t>
+          <t>Radnilombolo, Lu lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>751696.6837705269</v>
+        <v>751670</v>
       </c>
       <c r="R2" t="n">
-        <v>7424278.087885888</v>
+        <v>7424410</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -758,19 +753,9 @@
           <t>2016-09-29</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2016-09-29</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -798,15 +783,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>61639755</v>
+        <v>61639728</v>
       </c>
       <c r="B3" t="n">
-        <v>89611</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93185</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -814,36 +794,44 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5260</v>
+        <v>149</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lateritticka</t>
+          <t>Tallgråticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Postia lateritia</t>
+          <t>Boletopsis grisea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Renvall</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
+          <t>(Peck) Bondartsev &amp; Singer</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Stenbäcken, Lu lm</t>
+          <t>Radnilombolo, Lu lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>751637.5392023531</v>
+        <v>751670</v>
       </c>
       <c r="R3" t="n">
-        <v>7424360.524590464</v>
+        <v>7424410</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -873,19 +861,9 @@
           <t>2016-09-29</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2016-09-29</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -913,15 +891,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>61639777</v>
+        <v>61639788</v>
       </c>
       <c r="B4" t="n">
-        <v>90699</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93201</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -929,21 +902,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>232140</v>
+        <v>4365</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tajgataggsvamp</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellodon secretus</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Niemelä &amp; Kinnunen</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -963,10 +936,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>751696.6837705269</v>
+        <v>751697</v>
       </c>
       <c r="R4" t="n">
-        <v>7424278.087885888</v>
+        <v>7424278</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -996,19 +969,9 @@
           <t>2016-09-29</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2016-09-29</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1036,49 +999,36 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>61639728</v>
+        <v>61639730</v>
       </c>
       <c r="B5" t="n">
-        <v>90641</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93209</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>149</v>
+        <v>4366</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tallgråticka</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Boletopsis grisea</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Peck) Bondartsev &amp; Singer</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1086,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>751669.8442698084</v>
+        <v>751670</v>
       </c>
       <c r="R5" t="n">
-        <v>7424409.834793788</v>
+        <v>7424410</v>
       </c>
       <c r="S5" t="n">
         <v>50</v>
@@ -1119,19 +1069,9 @@
           <t>2016-09-29</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2016-09-29</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1159,37 +1099,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>61639719</v>
+        <v>61639784</v>
       </c>
       <c r="B6" t="n">
-        <v>89633</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>90522</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>65</v>
+        <v>4962</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Mjölsvärting</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Lyophyllum semitale</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Fr. : Fr.) Kühner</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1205,14 +1140,14 @@
       <c r="K6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Radnilombolo, Lu lm</t>
+          <t>Stenbäcken, Lu lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>751669.8442698084</v>
+        <v>751697</v>
       </c>
       <c r="R6" t="n">
-        <v>7424409.834793788</v>
+        <v>7424278</v>
       </c>
       <c r="S6" t="n">
         <v>50</v>
@@ -1242,19 +1177,9 @@
           <t>2016-09-29</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2016-09-29</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1282,15 +1207,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>61639788</v>
+        <v>61639755</v>
       </c>
       <c r="B7" t="n">
-        <v>90657</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92152</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1298,33 +1218,25 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4365</v>
+        <v>5260</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Lateritticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Postia lateritia</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>Renvall</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1332,10 +1244,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>751696.6837705269</v>
+        <v>751638</v>
       </c>
       <c r="R7" t="n">
-        <v>7424278.087885888</v>
+        <v>7424361</v>
       </c>
       <c r="S7" t="n">
         <v>50</v>
@@ -1365,19 +1277,9 @@
           <t>2016-09-29</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2016-09-29</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1405,15 +1307,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>61639730</v>
+        <v>61639749</v>
       </c>
       <c r="B8" t="n">
-        <v>90665</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91282</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1421,36 +1318,44 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4366</v>
+        <v>5685</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Gullgröppa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Pseudomerulius aureus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Banker</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
+          <t>(Fr.) Jülich</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Radnilombolo, Lu lm</t>
+          <t>Stenbäcken, Lu lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>751669.8442698084</v>
+        <v>751638</v>
       </c>
       <c r="R8" t="n">
-        <v>7424409.834793788</v>
+        <v>7424361</v>
       </c>
       <c r="S8" t="n">
         <v>50</v>
@@ -1480,19 +1385,9 @@
           <t>2016-09-29</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2016-09-29</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1520,63 +1415,48 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>61639677</v>
+        <v>120397453</v>
       </c>
       <c r="B9" t="n">
-        <v>90699</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57132</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>232140</v>
+        <v>102612</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tajgataggsvamp</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellodon secretus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Niemelä &amp; Kinnunen</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Radnilombolo, Lu lm</t>
+          <t>Nattavara, Lu lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>751669.8442698084</v>
+        <v>751652</v>
       </c>
       <c r="R9" t="n">
-        <v>7424409.834793788</v>
+        <v>7424472</v>
       </c>
       <c r="S9" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1600,22 +1480,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2016-09-29</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-07-23</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2016-09-29</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-07-23</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1624,56 +1494,50 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Lars Sundberg</t>
+          <t>Hanna Emanuelsson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Lars Sundberg, Sonja Kuoljok</t>
+          <t>Hanna Emanuelsson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>61639749</v>
+        <v>61639677</v>
       </c>
       <c r="B10" t="n">
-        <v>88806</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>93228</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5685</v>
+        <v>232140</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gullgröppa</t>
+          <t>Tajgataggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pseudomerulius aureus</t>
+          <t>Phellodon secretus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Jülich</t>
+          <t>Niemelä &amp; Kinnunen</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1689,14 +1553,14 @@
       <c r="K10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Stenbäcken, Lu lm</t>
+          <t>Radnilombolo, Lu lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>751637.5392023531</v>
+        <v>751670</v>
       </c>
       <c r="R10" t="n">
-        <v>7424360.524590464</v>
+        <v>7424410</v>
       </c>
       <c r="S10" t="n">
         <v>50</v>
@@ -1726,19 +1590,9 @@
           <t>2016-09-29</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2016-09-29</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1766,53 +1620,58 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120397453</v>
+        <v>61639777</v>
       </c>
       <c r="B11" t="n">
-        <v>56539</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93228</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>102612</v>
+        <v>232140</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tajgataggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Phellodon secretus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>Niemelä &amp; Kinnunen</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Nattavara, Lu lm</t>
+          <t>Stenbäcken, Lu lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>751652</v>
+        <v>751697</v>
       </c>
       <c r="R11" t="n">
-        <v>7424472</v>
+        <v>7424278</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1836,12 +1695,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2024-07-23</t>
+          <t>2016-09-29</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2024-07-23</t>
+          <t>2016-09-29</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1850,18 +1709,19 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Hanna Emanuelsson</t>
+          <t>Lars Sundberg</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Hanna Emanuelsson</t>
+          <t>Lars Sundberg, Sonja Kuoljok</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>

--- a/artfynd/A 36982-2023 artfynd.xlsx
+++ b/artfynd/A 36982-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AZ11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -780,6 +785,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61639719</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -888,6 +898,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61639728</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -996,6 +1011,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61639788</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1096,6 +1116,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61639730</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1204,6 +1229,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61639784</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1304,6 +1334,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61639755</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1412,6 +1447,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61639749</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1509,6 +1549,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120397453</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1617,6 +1662,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61639677</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1725,8 +1775,25 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61639777</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>